--- a/processed_accessions_b.gbk_anno.xlsx
+++ b/processed_accessions_b.gbk_anno.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/logan/Git-Repos/ICTVseqsearch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1A456C-FDFB-C347-837A-E47D1F07FCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C99FF1-1FFD-F645-A4EA-14BF30B6E6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="51200" windowHeight="26600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51340" yWindow="3860" windowWidth="38100" windowHeight="20680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,15 +41,6 @@
     <t>accession_id</t>
   </si>
   <si>
-    <t>organism</t>
-  </si>
-  <si>
-    <t>strain</t>
-  </si>
-  <si>
-    <t>isolation_source</t>
-  </si>
-  <si>
     <t>ICTV_ID</t>
   </si>
   <si>
@@ -134,40 +125,64 @@
     <t>isolate_designation</t>
   </si>
   <si>
+    <t>organism_gb</t>
+  </si>
+  <si>
+    <t>strain_gb</t>
+  </si>
+  <si>
+    <t>isolation_source_gb</t>
+  </si>
+  <si>
+    <t>ICTV20115492</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>AY954969</t>
+  </si>
+  <si>
+    <t>Duplodnaviria</t>
+  </si>
+  <si>
+    <t>Heunggongvirae</t>
+  </si>
+  <si>
+    <t>Uroviricota</t>
+  </si>
+  <si>
+    <t>Caudoviricetes</t>
+  </si>
+  <si>
+    <t>Herelleviridae</t>
+  </si>
+  <si>
+    <t>Twortvirinae</t>
+  </si>
+  <si>
+    <t>Kayvirus</t>
+  </si>
+  <si>
+    <t>Kayvirus G1</t>
+  </si>
+  <si>
     <t>Staphylococcus phage G1</t>
   </si>
   <si>
-    <t>ICTV20115492</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>AY954969</t>
-  </si>
-  <si>
-    <t>Duplodnaviria</t>
-  </si>
-  <si>
-    <t>Heunggongvirae</t>
-  </si>
-  <si>
-    <t>Uroviricota</t>
-  </si>
-  <si>
-    <t>Caudoviricetes</t>
-  </si>
-  <si>
-    <t>Herelleviridae</t>
-  </si>
-  <si>
-    <t>Twortvirinae</t>
-  </si>
-  <si>
-    <t>Kayvirus</t>
-  </si>
-  <si>
-    <t>Kayvirus G1</t>
+    <t>ICTV202319186</t>
+  </si>
+  <si>
+    <t>MK770119</t>
+  </si>
+  <si>
+    <t>Demerecviridae</t>
+  </si>
+  <si>
+    <t>Keyvirus</t>
+  </si>
+  <si>
+    <t>Keyvirus AAS21</t>
   </si>
   <si>
     <t>Pantoea phage vB_PagS_AAS21</t>
@@ -176,19 +191,16 @@
     <t>Ribes Jostabeere</t>
   </si>
   <si>
-    <t>ICTV202319186</t>
-  </si>
-  <si>
-    <t>MK770119</t>
-  </si>
-  <si>
-    <t>Demerecviridae</t>
-  </si>
-  <si>
-    <t>Keyvirus</t>
-  </si>
-  <si>
-    <t>Keyvirus AAS21</t>
+    <t>ICTV202319187</t>
+  </si>
+  <si>
+    <t>MZ616364</t>
+  </si>
+  <si>
+    <t>Keyvirus key</t>
+  </si>
+  <si>
+    <t>Erwinia phage Key</t>
   </si>
   <si>
     <t>Erwinia phage KEY</t>
@@ -197,138 +209,126 @@
     <t>fire blight affected quince and pear trees</t>
   </si>
   <si>
-    <t>ICTV202319187</t>
-  </si>
-  <si>
-    <t>MZ616364</t>
-  </si>
-  <si>
-    <t>Keyvirus key</t>
-  </si>
-  <si>
-    <t>Erwinia phage Key</t>
+    <t>ICTV20042222</t>
+  </si>
+  <si>
+    <t>HQ336222</t>
+  </si>
+  <si>
+    <t>Varidnaviria</t>
+  </si>
+  <si>
+    <t>Bamfordvirae</t>
+  </si>
+  <si>
+    <t>Nucleocytoviricota</t>
+  </si>
+  <si>
+    <t>Megaviricetes</t>
+  </si>
+  <si>
+    <t>Imitervirales</t>
+  </si>
+  <si>
+    <t>Mimiviridae</t>
+  </si>
+  <si>
+    <t>Megamimivirinae</t>
+  </si>
+  <si>
+    <t>Mimivirus</t>
+  </si>
+  <si>
+    <t>Mimivirus bradfordmassiliense</t>
   </si>
   <si>
     <t>Acanthamoeba polyphaga mimivirus</t>
   </si>
   <si>
-    <t>ICTV20042222</t>
-  </si>
-  <si>
-    <t>HQ336222</t>
-  </si>
-  <si>
-    <t>Varidnaviria</t>
-  </si>
-  <si>
-    <t>Bamfordvirae</t>
-  </si>
-  <si>
-    <t>Nucleocytoviricota</t>
-  </si>
-  <si>
-    <t>Megaviricetes</t>
-  </si>
-  <si>
-    <t>Imitervirales</t>
-  </si>
-  <si>
-    <t>Mimiviridae</t>
-  </si>
-  <si>
-    <t>Megamimivirinae</t>
-  </si>
-  <si>
-    <t>Mimivirus</t>
-  </si>
-  <si>
-    <t>Mimivirus bradfordmassiliense</t>
-  </si>
-  <si>
     <t>APMV</t>
   </si>
   <si>
+    <t>ICTV202318536</t>
+  </si>
+  <si>
+    <t>KT732816; KT732815; KT732817</t>
+  </si>
+  <si>
+    <t>Monodnaviria</t>
+  </si>
+  <si>
+    <t>Shotokuvirae</t>
+  </si>
+  <si>
+    <t>Cressdnaviricota</t>
+  </si>
+  <si>
+    <t>Arfiviricetes</t>
+  </si>
+  <si>
+    <t>Rohanvirales</t>
+  </si>
+  <si>
+    <t>Adamaviridae</t>
+  </si>
+  <si>
+    <t>Zirakzivirus</t>
+  </si>
+  <si>
+    <t>Zirakzivirus serni</t>
+  </si>
+  <si>
     <t>Pacific flying fox associated multicomponent virus</t>
   </si>
   <si>
+    <t>Tbat_K_12099</t>
+  </si>
+  <si>
     <t>feces</t>
   </si>
   <si>
-    <t>ICTV202318536</t>
-  </si>
-  <si>
-    <t>KT732816; KT732815; KT732817</t>
-  </si>
-  <si>
-    <t>Monodnaviria</t>
-  </si>
-  <si>
-    <t>Shotokuvirae</t>
-  </si>
-  <si>
-    <t>Cressdnaviricota</t>
-  </si>
-  <si>
-    <t>Arfiviricetes</t>
-  </si>
-  <si>
-    <t>Rohanvirales</t>
-  </si>
-  <si>
-    <t>Adamaviridae</t>
-  </si>
-  <si>
-    <t>Zirakzivirus</t>
-  </si>
-  <si>
-    <t>Zirakzivirus serni</t>
-  </si>
-  <si>
-    <t>Tbat_K_12099</t>
+    <t>ICTV19990689</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>L: HM119428; M: HM119429; S: HM119430</t>
+  </si>
+  <si>
+    <t>Riboviria</t>
+  </si>
+  <si>
+    <t>Orthornavirae</t>
+  </si>
+  <si>
+    <t>Negarnaviricota</t>
+  </si>
+  <si>
+    <t>Polyploviricotina</t>
+  </si>
+  <si>
+    <t>Bunyaviricetes</t>
+  </si>
+  <si>
+    <t>Hareavirales</t>
+  </si>
+  <si>
+    <t>Phenuiviridae</t>
+  </si>
+  <si>
+    <t>Phlebovirus</t>
+  </si>
+  <si>
+    <t>Phlebovirus candiruense</t>
   </si>
   <si>
     <t>Serra Norte virus</t>
   </si>
   <si>
-    <t>ICTV19990689</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>L: HM119428; M: HM119429; S: HM119430</t>
-  </si>
-  <si>
-    <t>Riboviria</t>
-  </si>
-  <si>
-    <t>Orthornavirae</t>
-  </si>
-  <si>
-    <t>Negarnaviricota</t>
-  </si>
-  <si>
-    <t>Polyploviricotina</t>
-  </si>
-  <si>
-    <t>Bunyaviricetes</t>
-  </si>
-  <si>
-    <t>Hareavirales</t>
-  </si>
-  <si>
-    <t>Phenuiviridae</t>
-  </si>
-  <si>
-    <t>Phlebovirus</t>
-  </si>
-  <si>
-    <t>Phlebovirus candiruense</t>
-  </si>
-  <si>
     <t>SNRV</t>
   </si>
   <si>
@@ -341,69 +341,69 @@
     <t>S</t>
   </si>
   <si>
+    <t>ICTV202420188</t>
+  </si>
+  <si>
+    <t>PP467602</t>
+  </si>
+  <si>
+    <t>Adnaviria</t>
+  </si>
+  <si>
+    <t>Zilligvirae</t>
+  </si>
+  <si>
+    <t>Taleaviricota</t>
+  </si>
+  <si>
+    <t>Tokiviricetes</t>
+  </si>
+  <si>
+    <t>Ligamenvirales</t>
+  </si>
+  <si>
+    <t>Chiyouviridae</t>
+  </si>
+  <si>
+    <t>Wargodvirus</t>
+  </si>
+  <si>
     <t>Wargodvirus xiongnu</t>
   </si>
   <si>
+    <t>Bathyarchaeia bifangarchaeales Chiyouvirus 1</t>
+  </si>
+  <si>
+    <t>BbCV1</t>
+  </si>
+  <si>
     <t>hot spring</t>
   </si>
   <si>
-    <t>ICTV202420188</t>
-  </si>
-  <si>
-    <t>PP467602</t>
-  </si>
-  <si>
-    <t>Adnaviria</t>
-  </si>
-  <si>
-    <t>Zilligvirae</t>
-  </si>
-  <si>
-    <t>Taleaviricota</t>
-  </si>
-  <si>
-    <t>Tokiviricetes</t>
-  </si>
-  <si>
-    <t>Ligamenvirales</t>
-  </si>
-  <si>
-    <t>Chiyouviridae</t>
-  </si>
-  <si>
-    <t>Wargodvirus</t>
-  </si>
-  <si>
-    <t>Bathyarchaeia bifangarchaeales Chiyouvirus 1</t>
-  </si>
-  <si>
-    <t>BbCV1</t>
+    <t>ICTV20020613</t>
+  </si>
+  <si>
+    <t>AF271059</t>
+  </si>
+  <si>
+    <t>Naldaviricetes</t>
+  </si>
+  <si>
+    <t>Lefavirales</t>
+  </si>
+  <si>
+    <t>Baculoviridae</t>
+  </si>
+  <si>
+    <t>Alphabaculovirus</t>
+  </si>
+  <si>
+    <t>Alphabaculovirus helarmigerae</t>
   </si>
   <si>
     <t>Helicoverpa armigera nucleopolyhedrovirus</t>
   </si>
   <si>
-    <t>ICTV20020613</t>
-  </si>
-  <si>
-    <t>AF271059</t>
-  </si>
-  <si>
-    <t>Naldaviricetes</t>
-  </si>
-  <si>
-    <t>Lefavirales</t>
-  </si>
-  <si>
-    <t>Baculoviridae</t>
-  </si>
-  <si>
-    <t>Alphabaculovirus</t>
-  </si>
-  <si>
-    <t>Alphabaculovirus helarmigerae</t>
-  </si>
-  <si>
     <t>HearNPV</t>
   </si>
   <si>
@@ -416,54 +416,54 @@
     <t>C1</t>
   </si>
   <si>
+    <t>AP010907</t>
+  </si>
+  <si>
+    <t>NNg1</t>
+  </si>
+  <si>
     <t>Helicoverpa armigera NPV NNg1</t>
   </si>
   <si>
-    <t>NNg1</t>
-  </si>
-  <si>
-    <t>AP010907</t>
+    <t>ICTV20042009</t>
+  </si>
+  <si>
+    <t>Seg1</t>
+  </si>
+  <si>
+    <t>Seg1: AY317099; Seg2: AY317100; Seg3: AY317101; Seg4: AY317102; Seg5: AY317103; Seg6: AY317104; Seg7: AY317105; Seg8: AY317106; Seg9: AY317107; Seg10: AY317108; Seg11: AY317109; Seg12: AY317110</t>
+  </si>
+  <si>
+    <t>Duplornaviricota</t>
+  </si>
+  <si>
+    <t>Resentoviricetes</t>
+  </si>
+  <si>
+    <t>Reovirales</t>
+  </si>
+  <si>
+    <t>Sedoreoviridae</t>
+  </si>
+  <si>
+    <t>Seadornavirus</t>
+  </si>
+  <si>
+    <t>Seadornavirus liaoningense</t>
   </si>
   <si>
     <t>Liao ning virus</t>
   </si>
   <si>
+    <t>LNV</t>
+  </si>
+  <si>
+    <t>NE9731</t>
+  </si>
+  <si>
     <t>LNSV-NE97-31</t>
   </si>
   <si>
-    <t>ICTV20042009</t>
-  </si>
-  <si>
-    <t>Seg1</t>
-  </si>
-  <si>
-    <t>Seg1: AY317099; Seg2: AY317100; Seg3: AY317101; Seg4: AY317102; Seg5: AY317103; Seg6: AY317104; Seg7: AY317105; Seg8: AY317106; Seg9: AY317107; Seg10: AY317108; Seg11: AY317109; Seg12: AY317110</t>
-  </si>
-  <si>
-    <t>Duplornaviricota</t>
-  </si>
-  <si>
-    <t>Resentoviricetes</t>
-  </si>
-  <si>
-    <t>Reovirales</t>
-  </si>
-  <si>
-    <t>Sedoreoviridae</t>
-  </si>
-  <si>
-    <t>Seadornavirus</t>
-  </si>
-  <si>
-    <t>Seadornavirus liaoningense</t>
-  </si>
-  <si>
-    <t>LNV</t>
-  </si>
-  <si>
-    <t>NE9731</t>
-  </si>
-  <si>
     <t>Seg2</t>
   </si>
   <si>
@@ -497,28 +497,28 @@
     <t>Seg12</t>
   </si>
   <si>
+    <t>ICTV20115504</t>
+  </si>
+  <si>
+    <t>AE006468 (2844298.2877981)</t>
+  </si>
+  <si>
+    <t>Peduoviridae</t>
+  </si>
+  <si>
+    <t>Felsduovirus</t>
+  </si>
+  <si>
+    <t>Felsduovirus Fels2</t>
+  </si>
+  <si>
+    <t>Salmonella phage Fels2</t>
+  </si>
+  <si>
     <t>Salmonella enterica subsp. enterica serovar Typhimurium str. LT2, Salmonella virus Fels2</t>
   </si>
   <si>
     <t>LT2</t>
-  </si>
-  <si>
-    <t>ICTV20115504</t>
-  </si>
-  <si>
-    <t>AE006468 (2844298.2877981)</t>
-  </si>
-  <si>
-    <t>Peduoviridae</t>
-  </si>
-  <si>
-    <t>Felsduovirus</t>
-  </si>
-  <si>
-    <t>Felsduovirus Fels2</t>
-  </si>
-  <si>
-    <t>Salmonella phage Fels2</t>
   </si>
 </sst>
 </file>
@@ -863,36 +863,36 @@
   <cols>
     <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="69.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="164.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="164.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="69.1640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="31.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.2">
@@ -1008,50 +1008,50 @@
       <c r="C2" t="s">
         <v>33</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D2" t="s">
         <v>34</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2673</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
         <v>35</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2673</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="M2" t="s">
         <v>36</v>
       </c>
-      <c r="P2" t="s">
+      <c r="O2" t="s">
         <v>37</v>
       </c>
-      <c r="R2" t="s">
+      <c r="Q2" t="s">
         <v>38</v>
       </c>
-      <c r="T2" t="s">
+      <c r="S2" t="s">
         <v>39</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>40</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="X2" t="s">
         <v>41</v>
       </c>
+      <c r="Y2" t="s">
+        <v>42</v>
+      </c>
       <c r="AA2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AB2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD2" t="s">
         <v>44</v>
       </c>
       <c r="AE2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.2">
@@ -1066,50 +1066,50 @@
       <c r="C3" t="s">
         <v>45</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2253</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
         <v>46</v>
       </c>
-      <c r="F3" t="s">
+      <c r="M3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W3" t="s">
         <v>47</v>
       </c>
-      <c r="G3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>2253</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="Y3" t="s">
         <v>48</v>
       </c>
-      <c r="P3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R3" t="s">
-        <v>38</v>
-      </c>
-      <c r="T3" t="s">
-        <v>39</v>
-      </c>
-      <c r="V3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
         <v>49</v>
       </c>
       <c r="AB3" t="s">
         <v>50</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AE3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG3" t="s">
         <v>51</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.2">
@@ -1124,49 +1124,49 @@
       <c r="C4" t="s">
         <v>52</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2254</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
         <v>53</v>
       </c>
-      <c r="F4" t="s">
+      <c r="M4" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>38</v>
+      </c>
+      <c r="S4" t="s">
+        <v>39</v>
+      </c>
+      <c r="W4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA4" t="s">
         <v>54</v>
       </c>
-      <c r="G4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>2254</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="AB4" t="s">
         <v>55</v>
       </c>
-      <c r="P4" t="s">
-        <v>37</v>
-      </c>
-      <c r="R4" t="s">
-        <v>38</v>
-      </c>
-      <c r="T4" t="s">
-        <v>39</v>
-      </c>
-      <c r="V4" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>56</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AG4" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1182,56 +1182,56 @@
       <c r="C5" t="s">
         <v>58</v>
       </c>
-      <c r="F5" t="s">
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>15476</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
         <v>59</v>
       </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>15476</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="M5" t="s">
         <v>60</v>
       </c>
-      <c r="P5" t="s">
+      <c r="O5" t="s">
         <v>61</v>
       </c>
-      <c r="R5" t="s">
+      <c r="Q5" t="s">
         <v>62</v>
       </c>
-      <c r="T5" t="s">
+      <c r="S5" t="s">
         <v>63</v>
       </c>
-      <c r="V5" t="s">
+      <c r="U5" t="s">
         <v>64</v>
       </c>
+      <c r="W5" t="s">
+        <v>65</v>
+      </c>
       <c r="X5" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z5" t="s">
         <v>66</v>
       </c>
+      <c r="Y5" t="s">
+        <v>67</v>
+      </c>
       <c r="AA5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AB5" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD5" t="s">
         <v>69</v>
       </c>
+      <c r="AC5" t="s">
+        <v>70</v>
+      </c>
       <c r="AE5" t="s">
-        <v>58</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.2">
@@ -1246,43 +1246,43 @@
       <c r="C6" t="s">
         <v>71</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>7395</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
         <v>72</v>
       </c>
-      <c r="F6" t="s">
+      <c r="M6" t="s">
         <v>73</v>
       </c>
-      <c r="G6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>7395</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>74</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>75</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>76</v>
       </c>
-      <c r="T6" t="s">
+      <c r="U6" t="s">
         <v>77</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>78</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Y6" t="s">
         <v>79</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AA6" t="s">
         <v>80</v>
       </c>
       <c r="AB6" t="s">
@@ -1292,7 +1292,7 @@
         <v>82</v>
       </c>
       <c r="AE6" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AG6" t="s">
         <v>83</v>
@@ -1310,43 +1310,43 @@
       <c r="C7" t="s">
         <v>71</v>
       </c>
-      <c r="E7" t="s">
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>7395</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
         <v>72</v>
       </c>
-      <c r="F7" t="s">
+      <c r="M7" t="s">
         <v>73</v>
       </c>
-      <c r="G7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="L7">
-        <v>7395</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>74</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>75</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>76</v>
       </c>
-      <c r="T7" t="s">
+      <c r="U7" t="s">
         <v>77</v>
       </c>
-      <c r="V7" t="s">
+      <c r="W7" t="s">
         <v>78</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Y7" t="s">
         <v>79</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AA7" t="s">
         <v>80</v>
       </c>
       <c r="AB7" t="s">
@@ -1356,7 +1356,7 @@
         <v>82</v>
       </c>
       <c r="AE7" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AG7" t="s">
         <v>83</v>
@@ -1374,43 +1374,43 @@
       <c r="C8" t="s">
         <v>71</v>
       </c>
-      <c r="E8" t="s">
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="I8">
+        <v>7395</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
         <v>72</v>
       </c>
-      <c r="F8" t="s">
+      <c r="M8" t="s">
         <v>73</v>
       </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="L8">
-        <v>7395</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="O8" t="s">
         <v>74</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>75</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>76</v>
       </c>
-      <c r="T8" t="s">
+      <c r="U8" t="s">
         <v>77</v>
       </c>
-      <c r="V8" t="s">
+      <c r="W8" t="s">
         <v>78</v>
       </c>
-      <c r="X8" t="s">
+      <c r="Y8" t="s">
         <v>79</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="AA8" t="s">
         <v>80</v>
       </c>
       <c r="AB8" t="s">
@@ -1420,7 +1420,7 @@
         <v>82</v>
       </c>
       <c r="AE8" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AG8" t="s">
         <v>83</v>
@@ -1438,62 +1438,62 @@
       <c r="C9" t="s">
         <v>84</v>
       </c>
+      <c r="D9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
       <c r="F9" t="s">
-        <v>85</v>
-      </c>
-      <c r="G9" t="s">
         <v>86</v>
       </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="I9">
+        <v>13851</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+      <c r="K9" t="s">
         <v>87</v>
       </c>
-      <c r="L9">
-        <v>13851</v>
-      </c>
-      <c r="M9">
-        <v>6</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="M9" t="s">
         <v>88</v>
       </c>
-      <c r="P9" t="s">
+      <c r="O9" t="s">
         <v>89</v>
       </c>
+      <c r="Q9" t="s">
+        <v>90</v>
+      </c>
       <c r="R9" t="s">
-        <v>90</v>
-      </c>
-      <c r="T9" t="s">
         <v>91</v>
       </c>
+      <c r="S9" t="s">
+        <v>92</v>
+      </c>
       <c r="U9" t="s">
-        <v>92</v>
-      </c>
-      <c r="V9" t="s">
         <v>93</v>
       </c>
-      <c r="X9" t="s">
+      <c r="W9" t="s">
         <v>94</v>
       </c>
-      <c r="Z9" t="s">
+      <c r="Y9" t="s">
         <v>95</v>
       </c>
+      <c r="AA9" t="s">
+        <v>96</v>
+      </c>
       <c r="AB9" t="s">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>98</v>
       </c>
       <c r="AD9" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE9" t="s">
         <v>97</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.2">
@@ -1508,62 +1508,62 @@
       <c r="C10" t="s">
         <v>84</v>
       </c>
+      <c r="D10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
       <c r="F10" t="s">
-        <v>85</v>
-      </c>
-      <c r="G10" t="s">
-        <v>86</v>
-      </c>
-      <c r="H10">
-        <v>2</v>
-      </c>
-      <c r="I10" t="s">
         <v>100</v>
       </c>
-      <c r="L10">
+      <c r="I10">
         <v>13851</v>
       </c>
-      <c r="M10">
+      <c r="J10">
         <v>6</v>
       </c>
-      <c r="N10" t="s">
+      <c r="K10" t="s">
+        <v>87</v>
+      </c>
+      <c r="M10" t="s">
         <v>88</v>
       </c>
-      <c r="P10" t="s">
+      <c r="O10" t="s">
         <v>89</v>
       </c>
+      <c r="Q10" t="s">
+        <v>90</v>
+      </c>
       <c r="R10" t="s">
-        <v>90</v>
-      </c>
-      <c r="T10" t="s">
         <v>91</v>
       </c>
+      <c r="S10" t="s">
+        <v>92</v>
+      </c>
       <c r="U10" t="s">
-        <v>92</v>
-      </c>
-      <c r="V10" t="s">
         <v>93</v>
       </c>
-      <c r="X10" t="s">
+      <c r="W10" t="s">
         <v>94</v>
       </c>
-      <c r="Z10" t="s">
+      <c r="Y10" t="s">
         <v>95</v>
       </c>
+      <c r="AA10" t="s">
+        <v>96</v>
+      </c>
       <c r="AB10" t="s">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>98</v>
       </c>
       <c r="AD10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE10" t="s">
         <v>97</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.2">
@@ -1578,62 +1578,62 @@
       <c r="C11" t="s">
         <v>84</v>
       </c>
+      <c r="D11" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
       <c r="F11" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11">
-        <v>3</v>
-      </c>
-      <c r="I11" t="s">
         <v>101</v>
       </c>
-      <c r="L11">
+      <c r="I11">
         <v>13851</v>
       </c>
-      <c r="M11">
+      <c r="J11">
         <v>6</v>
       </c>
-      <c r="N11" t="s">
+      <c r="K11" t="s">
+        <v>87</v>
+      </c>
+      <c r="M11" t="s">
         <v>88</v>
       </c>
-      <c r="P11" t="s">
+      <c r="O11" t="s">
         <v>89</v>
       </c>
+      <c r="Q11" t="s">
+        <v>90</v>
+      </c>
       <c r="R11" t="s">
-        <v>90</v>
-      </c>
-      <c r="T11" t="s">
         <v>91</v>
       </c>
+      <c r="S11" t="s">
+        <v>92</v>
+      </c>
       <c r="U11" t="s">
-        <v>92</v>
-      </c>
-      <c r="V11" t="s">
         <v>93</v>
       </c>
-      <c r="X11" t="s">
+      <c r="W11" t="s">
         <v>94</v>
       </c>
-      <c r="Z11" t="s">
+      <c r="Y11" t="s">
         <v>95</v>
       </c>
+      <c r="AA11" t="s">
+        <v>96</v>
+      </c>
       <c r="AB11" t="s">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>98</v>
       </c>
       <c r="AD11" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE11" t="s">
         <v>97</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.2">
@@ -1648,55 +1648,55 @@
       <c r="C12" t="s">
         <v>102</v>
       </c>
-      <c r="E12" t="s">
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
         <v>103</v>
       </c>
-      <c r="F12" t="s">
+      <c r="M12" t="s">
         <v>104</v>
       </c>
-      <c r="G12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>105</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>106</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
         <v>107</v>
       </c>
-      <c r="T12" t="s">
+      <c r="U12" t="s">
         <v>108</v>
       </c>
-      <c r="V12" t="s">
+      <c r="W12" t="s">
         <v>109</v>
       </c>
-      <c r="X12" t="s">
+      <c r="Y12" t="s">
         <v>110</v>
       </c>
-      <c r="Z12" t="s">
+      <c r="AA12" t="s">
         <v>111</v>
       </c>
       <c r="AB12" t="s">
         <v>112</v>
       </c>
-      <c r="AD12" t="s">
-        <v>102</v>
+      <c r="AC12" t="s">
+        <v>113</v>
       </c>
       <c r="AE12" t="s">
-        <v>113</v>
-      </c>
-      <c r="AF12" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG12" t="s">
         <v>114</v>
       </c>
     </row>
@@ -1712,47 +1712,47 @@
       <c r="C13" t="s">
         <v>115</v>
       </c>
-      <c r="F13" t="s">
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>15762</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13" t="s">
         <v>116</v>
       </c>
-      <c r="G13" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="L13">
-        <v>15762</v>
-      </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="N13" t="s">
+      <c r="S13" t="s">
         <v>117</v>
       </c>
-      <c r="V13" t="s">
+      <c r="U13" t="s">
         <v>118</v>
       </c>
-      <c r="X13" t="s">
+      <c r="W13" t="s">
         <v>119</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="Y13" t="s">
         <v>120</v>
       </c>
+      <c r="AA13" t="s">
+        <v>121</v>
+      </c>
       <c r="AB13" t="s">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>123</v>
       </c>
       <c r="AD13" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE13" t="s">
         <v>122</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>115</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>123</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.2">
@@ -1767,47 +1767,47 @@
       <c r="C14" t="s">
         <v>115</v>
       </c>
-      <c r="F14" t="s">
-        <v>116</v>
-      </c>
-      <c r="G14" t="s">
-        <v>86</v>
-      </c>
-      <c r="H14">
+      <c r="D14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14">
         <v>1</v>
       </c>
-      <c r="L14">
+      <c r="I14">
         <v>15762</v>
       </c>
-      <c r="M14">
+      <c r="J14">
         <v>2</v>
       </c>
-      <c r="N14" t="s">
+      <c r="K14" t="s">
         <v>125</v>
       </c>
-      <c r="V14" t="s">
+      <c r="S14" t="s">
+        <v>117</v>
+      </c>
+      <c r="U14" t="s">
         <v>118</v>
       </c>
-      <c r="X14" t="s">
+      <c r="W14" t="s">
         <v>119</v>
       </c>
-      <c r="Z14" t="s">
+      <c r="Y14" t="s">
         <v>120</v>
       </c>
+      <c r="AA14" t="s">
+        <v>121</v>
+      </c>
       <c r="AB14" t="s">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>123</v>
       </c>
       <c r="AD14" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE14" t="s">
         <v>122</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>115</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>123</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.2">
@@ -1820,51 +1820,51 @@
         <v>AP010907</v>
       </c>
       <c r="C15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>15762</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15" t="s">
         <v>127</v>
       </c>
-      <c r="D15" t="s">
+      <c r="S15" t="s">
+        <v>117</v>
+      </c>
+      <c r="U15" t="s">
+        <v>118</v>
+      </c>
+      <c r="W15" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD15" t="s">
         <v>128</v>
       </c>
-      <c r="F15" t="s">
-        <v>116</v>
-      </c>
-      <c r="G15" t="s">
-        <v>86</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="L15">
-        <v>15762</v>
-      </c>
-      <c r="M15">
-        <v>3</v>
-      </c>
-      <c r="N15" t="s">
+      <c r="AE15" t="s">
         <v>129</v>
       </c>
-      <c r="V15" t="s">
-        <v>118</v>
-      </c>
-      <c r="X15" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>115</v>
-      </c>
       <c r="AF15" t="s">
-        <v>123</v>
-      </c>
-      <c r="AG15" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1881,64 +1881,64 @@
         <v>130</v>
       </c>
       <c r="D16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
         <v>131</v>
       </c>
-      <c r="F16" t="s">
+      <c r="I16">
+        <v>8654</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16" t="s">
         <v>132</v>
       </c>
-      <c r="G16" t="s">
-        <v>86</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="M16" t="s">
+        <v>88</v>
+      </c>
+      <c r="O16" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q16" t="s">
         <v>133</v>
       </c>
-      <c r="L16">
-        <v>8654</v>
-      </c>
-      <c r="M16">
-        <v>2</v>
-      </c>
-      <c r="N16" t="s">
+      <c r="S16" t="s">
         <v>134</v>
       </c>
-      <c r="P16" t="s">
-        <v>89</v>
-      </c>
-      <c r="R16" t="s">
-        <v>90</v>
-      </c>
-      <c r="T16" t="s">
+      <c r="U16" t="s">
         <v>135</v>
       </c>
-      <c r="V16" t="s">
+      <c r="W16" t="s">
         <v>136</v>
       </c>
-      <c r="X16" t="s">
+      <c r="Y16" t="s">
         <v>137</v>
       </c>
-      <c r="Z16" t="s">
+      <c r="AA16" t="s">
         <v>138</v>
       </c>
       <c r="AB16" t="s">
         <v>139</v>
       </c>
+      <c r="AC16" t="s">
+        <v>140</v>
+      </c>
       <c r="AD16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AE16" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AF16" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG16" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>VMR1012711</v>
@@ -1951,64 +1951,64 @@
         <v>130</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>85</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
       </c>
       <c r="F17" t="s">
+        <v>143</v>
+      </c>
+      <c r="I17">
+        <v>8654</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17" t="s">
         <v>132</v>
       </c>
-      <c r="G17" t="s">
-        <v>86</v>
-      </c>
-      <c r="H17">
-        <v>2</v>
-      </c>
-      <c r="I17" t="s">
-        <v>143</v>
-      </c>
-      <c r="L17">
-        <v>8654</v>
-      </c>
-      <c r="M17">
-        <v>2</v>
-      </c>
-      <c r="N17" t="s">
+      <c r="M17" t="s">
+        <v>88</v>
+      </c>
+      <c r="O17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>133</v>
+      </c>
+      <c r="S17" t="s">
         <v>134</v>
       </c>
-      <c r="P17" t="s">
-        <v>89</v>
-      </c>
-      <c r="R17" t="s">
-        <v>90</v>
-      </c>
-      <c r="T17" t="s">
+      <c r="U17" t="s">
         <v>135</v>
       </c>
-      <c r="V17" t="s">
+      <c r="W17" t="s">
         <v>136</v>
       </c>
-      <c r="X17" t="s">
+      <c r="Y17" t="s">
         <v>137</v>
       </c>
-      <c r="Z17" t="s">
+      <c r="AA17" t="s">
         <v>138</v>
       </c>
       <c r="AB17" t="s">
         <v>139</v>
       </c>
+      <c r="AC17" t="s">
+        <v>140</v>
+      </c>
       <c r="AD17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AE17" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AF17" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG17" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>VMR1012711</v>
@@ -2021,64 +2021,64 @@
         <v>130</v>
       </c>
       <c r="D18" t="s">
-        <v>131</v>
+        <v>85</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
       </c>
       <c r="F18" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18">
+        <v>8654</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18" t="s">
         <v>132</v>
       </c>
-      <c r="G18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H18">
-        <v>3</v>
-      </c>
-      <c r="I18" t="s">
-        <v>144</v>
-      </c>
-      <c r="L18">
-        <v>8654</v>
-      </c>
-      <c r="M18">
-        <v>2</v>
-      </c>
-      <c r="N18" t="s">
+      <c r="M18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O18" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>133</v>
+      </c>
+      <c r="S18" t="s">
         <v>134</v>
       </c>
-      <c r="P18" t="s">
-        <v>89</v>
-      </c>
-      <c r="R18" t="s">
-        <v>90</v>
-      </c>
-      <c r="T18" t="s">
+      <c r="U18" t="s">
         <v>135</v>
       </c>
-      <c r="V18" t="s">
+      <c r="W18" t="s">
         <v>136</v>
       </c>
-      <c r="X18" t="s">
+      <c r="Y18" t="s">
         <v>137</v>
       </c>
-      <c r="Z18" t="s">
+      <c r="AA18" t="s">
         <v>138</v>
       </c>
       <c r="AB18" t="s">
         <v>139</v>
       </c>
+      <c r="AC18" t="s">
+        <v>140</v>
+      </c>
       <c r="AD18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AE18" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AF18" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG18" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>VMR1012711</v>
@@ -2091,64 +2091,64 @@
         <v>130</v>
       </c>
       <c r="D19" t="s">
-        <v>131</v>
+        <v>85</v>
+      </c>
+      <c r="E19">
+        <v>4</v>
       </c>
       <c r="F19" t="s">
+        <v>145</v>
+      </c>
+      <c r="I19">
+        <v>8654</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19" t="s">
         <v>132</v>
       </c>
-      <c r="G19" t="s">
-        <v>86</v>
-      </c>
-      <c r="H19">
-        <v>4</v>
-      </c>
-      <c r="I19" t="s">
-        <v>145</v>
-      </c>
-      <c r="L19">
-        <v>8654</v>
-      </c>
-      <c r="M19">
-        <v>2</v>
-      </c>
-      <c r="N19" t="s">
+      <c r="M19" t="s">
+        <v>88</v>
+      </c>
+      <c r="O19" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>133</v>
+      </c>
+      <c r="S19" t="s">
         <v>134</v>
       </c>
-      <c r="P19" t="s">
-        <v>89</v>
-      </c>
-      <c r="R19" t="s">
-        <v>90</v>
-      </c>
-      <c r="T19" t="s">
+      <c r="U19" t="s">
         <v>135</v>
       </c>
-      <c r="V19" t="s">
+      <c r="W19" t="s">
         <v>136</v>
       </c>
-      <c r="X19" t="s">
+      <c r="Y19" t="s">
         <v>137</v>
       </c>
-      <c r="Z19" t="s">
+      <c r="AA19" t="s">
         <v>138</v>
       </c>
       <c r="AB19" t="s">
         <v>139</v>
       </c>
+      <c r="AC19" t="s">
+        <v>140</v>
+      </c>
       <c r="AD19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AE19" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AF19" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG19" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
         <f t="shared" si="0"/>
         <v>VMR1012711</v>
@@ -2161,64 +2161,64 @@
         <v>130</v>
       </c>
       <c r="D20" t="s">
-        <v>131</v>
+        <v>85</v>
+      </c>
+      <c r="E20">
+        <v>5</v>
       </c>
       <c r="F20" t="s">
+        <v>146</v>
+      </c>
+      <c r="I20">
+        <v>8654</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+      <c r="K20" t="s">
         <v>132</v>
       </c>
-      <c r="G20" t="s">
-        <v>86</v>
-      </c>
-      <c r="H20">
-        <v>5</v>
-      </c>
-      <c r="I20" t="s">
-        <v>146</v>
-      </c>
-      <c r="L20">
-        <v>8654</v>
-      </c>
-      <c r="M20">
-        <v>2</v>
-      </c>
-      <c r="N20" t="s">
+      <c r="M20" t="s">
+        <v>88</v>
+      </c>
+      <c r="O20" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>133</v>
+      </c>
+      <c r="S20" t="s">
         <v>134</v>
       </c>
-      <c r="P20" t="s">
-        <v>89</v>
-      </c>
-      <c r="R20" t="s">
-        <v>90</v>
-      </c>
-      <c r="T20" t="s">
+      <c r="U20" t="s">
         <v>135</v>
       </c>
-      <c r="V20" t="s">
+      <c r="W20" t="s">
         <v>136</v>
       </c>
-      <c r="X20" t="s">
+      <c r="Y20" t="s">
         <v>137</v>
       </c>
-      <c r="Z20" t="s">
+      <c r="AA20" t="s">
         <v>138</v>
       </c>
       <c r="AB20" t="s">
         <v>139</v>
       </c>
+      <c r="AC20" t="s">
+        <v>140</v>
+      </c>
       <c r="AD20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AE20" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AF20" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG20" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>VMR1012711</v>
@@ -2231,64 +2231,64 @@
         <v>130</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>85</v>
+      </c>
+      <c r="E21">
+        <v>6</v>
       </c>
       <c r="F21" t="s">
+        <v>147</v>
+      </c>
+      <c r="I21">
+        <v>8654</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21" t="s">
         <v>132</v>
       </c>
-      <c r="G21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H21">
-        <v>6</v>
-      </c>
-      <c r="I21" t="s">
-        <v>147</v>
-      </c>
-      <c r="L21">
-        <v>8654</v>
-      </c>
-      <c r="M21">
-        <v>2</v>
-      </c>
-      <c r="N21" t="s">
+      <c r="M21" t="s">
+        <v>88</v>
+      </c>
+      <c r="O21" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>133</v>
+      </c>
+      <c r="S21" t="s">
         <v>134</v>
       </c>
-      <c r="P21" t="s">
-        <v>89</v>
-      </c>
-      <c r="R21" t="s">
-        <v>90</v>
-      </c>
-      <c r="T21" t="s">
+      <c r="U21" t="s">
         <v>135</v>
       </c>
-      <c r="V21" t="s">
+      <c r="W21" t="s">
         <v>136</v>
       </c>
-      <c r="X21" t="s">
+      <c r="Y21" t="s">
         <v>137</v>
       </c>
-      <c r="Z21" t="s">
+      <c r="AA21" t="s">
         <v>138</v>
       </c>
       <c r="AB21" t="s">
         <v>139</v>
       </c>
+      <c r="AC21" t="s">
+        <v>140</v>
+      </c>
       <c r="AD21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AE21" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AF21" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG21" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>VMR1012711</v>
@@ -2301,64 +2301,64 @@
         <v>130</v>
       </c>
       <c r="D22" t="s">
-        <v>131</v>
+        <v>85</v>
+      </c>
+      <c r="E22">
+        <v>7</v>
       </c>
       <c r="F22" t="s">
+        <v>148</v>
+      </c>
+      <c r="I22">
+        <v>8654</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22" t="s">
         <v>132</v>
       </c>
-      <c r="G22" t="s">
-        <v>86</v>
-      </c>
-      <c r="H22">
-        <v>7</v>
-      </c>
-      <c r="I22" t="s">
-        <v>148</v>
-      </c>
-      <c r="L22">
-        <v>8654</v>
-      </c>
-      <c r="M22">
-        <v>2</v>
-      </c>
-      <c r="N22" t="s">
+      <c r="M22" t="s">
+        <v>88</v>
+      </c>
+      <c r="O22" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>133</v>
+      </c>
+      <c r="S22" t="s">
         <v>134</v>
       </c>
-      <c r="P22" t="s">
-        <v>89</v>
-      </c>
-      <c r="R22" t="s">
-        <v>90</v>
-      </c>
-      <c r="T22" t="s">
+      <c r="U22" t="s">
         <v>135</v>
       </c>
-      <c r="V22" t="s">
+      <c r="W22" t="s">
         <v>136</v>
       </c>
-      <c r="X22" t="s">
+      <c r="Y22" t="s">
         <v>137</v>
       </c>
-      <c r="Z22" t="s">
+      <c r="AA22" t="s">
         <v>138</v>
       </c>
       <c r="AB22" t="s">
         <v>139</v>
       </c>
+      <c r="AC22" t="s">
+        <v>140</v>
+      </c>
       <c r="AD22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AE22" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AF22" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG22" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>VMR1012711</v>
@@ -2371,64 +2371,64 @@
         <v>130</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>85</v>
+      </c>
+      <c r="E23">
+        <v>8</v>
       </c>
       <c r="F23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I23">
+        <v>8654</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+      <c r="K23" t="s">
         <v>132</v>
       </c>
-      <c r="G23" t="s">
-        <v>86</v>
-      </c>
-      <c r="H23">
-        <v>8</v>
-      </c>
-      <c r="I23" t="s">
-        <v>149</v>
-      </c>
-      <c r="L23">
-        <v>8654</v>
-      </c>
-      <c r="M23">
-        <v>2</v>
-      </c>
-      <c r="N23" t="s">
+      <c r="M23" t="s">
+        <v>88</v>
+      </c>
+      <c r="O23" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>133</v>
+      </c>
+      <c r="S23" t="s">
         <v>134</v>
       </c>
-      <c r="P23" t="s">
-        <v>89</v>
-      </c>
-      <c r="R23" t="s">
-        <v>90</v>
-      </c>
-      <c r="T23" t="s">
+      <c r="U23" t="s">
         <v>135</v>
       </c>
-      <c r="V23" t="s">
+      <c r="W23" t="s">
         <v>136</v>
       </c>
-      <c r="X23" t="s">
+      <c r="Y23" t="s">
         <v>137</v>
       </c>
-      <c r="Z23" t="s">
+      <c r="AA23" t="s">
         <v>138</v>
       </c>
       <c r="AB23" t="s">
         <v>139</v>
       </c>
+      <c r="AC23" t="s">
+        <v>140</v>
+      </c>
       <c r="AD23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AE23" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AF23" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG23" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
         <f t="shared" si="0"/>
         <v>VMR1012711</v>
@@ -2441,64 +2441,64 @@
         <v>130</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>85</v>
+      </c>
+      <c r="E24">
+        <v>9</v>
       </c>
       <c r="F24" t="s">
+        <v>150</v>
+      </c>
+      <c r="I24">
+        <v>8654</v>
+      </c>
+      <c r="J24">
+        <v>2</v>
+      </c>
+      <c r="K24" t="s">
         <v>132</v>
       </c>
-      <c r="G24" t="s">
-        <v>86</v>
-      </c>
-      <c r="H24">
-        <v>9</v>
-      </c>
-      <c r="I24" t="s">
-        <v>150</v>
-      </c>
-      <c r="L24">
-        <v>8654</v>
-      </c>
-      <c r="M24">
-        <v>2</v>
-      </c>
-      <c r="N24" t="s">
+      <c r="M24" t="s">
+        <v>88</v>
+      </c>
+      <c r="O24" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>133</v>
+      </c>
+      <c r="S24" t="s">
         <v>134</v>
       </c>
-      <c r="P24" t="s">
-        <v>89</v>
-      </c>
-      <c r="R24" t="s">
-        <v>90</v>
-      </c>
-      <c r="T24" t="s">
+      <c r="U24" t="s">
         <v>135</v>
       </c>
-      <c r="V24" t="s">
+      <c r="W24" t="s">
         <v>136</v>
       </c>
-      <c r="X24" t="s">
+      <c r="Y24" t="s">
         <v>137</v>
       </c>
-      <c r="Z24" t="s">
+      <c r="AA24" t="s">
         <v>138</v>
       </c>
       <c r="AB24" t="s">
         <v>139</v>
       </c>
+      <c r="AC24" t="s">
+        <v>140</v>
+      </c>
       <c r="AD24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AE24" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AF24" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG24" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
         <f t="shared" si="0"/>
         <v>VMR1012711</v>
@@ -2511,64 +2511,64 @@
         <v>130</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>85</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
       </c>
       <c r="F25" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25">
+        <v>8654</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25" t="s">
         <v>132</v>
       </c>
-      <c r="G25" t="s">
-        <v>86</v>
-      </c>
-      <c r="H25">
-        <v>10</v>
-      </c>
-      <c r="I25" t="s">
-        <v>151</v>
-      </c>
-      <c r="L25">
-        <v>8654</v>
-      </c>
-      <c r="M25">
-        <v>2</v>
-      </c>
-      <c r="N25" t="s">
+      <c r="M25" t="s">
+        <v>88</v>
+      </c>
+      <c r="O25" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>133</v>
+      </c>
+      <c r="S25" t="s">
         <v>134</v>
       </c>
-      <c r="P25" t="s">
-        <v>89</v>
-      </c>
-      <c r="R25" t="s">
-        <v>90</v>
-      </c>
-      <c r="T25" t="s">
+      <c r="U25" t="s">
         <v>135</v>
       </c>
-      <c r="V25" t="s">
+      <c r="W25" t="s">
         <v>136</v>
       </c>
-      <c r="X25" t="s">
+      <c r="Y25" t="s">
         <v>137</v>
       </c>
-      <c r="Z25" t="s">
+      <c r="AA25" t="s">
         <v>138</v>
       </c>
       <c r="AB25" t="s">
         <v>139</v>
       </c>
+      <c r="AC25" t="s">
+        <v>140</v>
+      </c>
       <c r="AD25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AE25" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AF25" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG25" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
         <f t="shared" si="0"/>
         <v>VMR1012711</v>
@@ -2581,64 +2581,64 @@
         <v>130</v>
       </c>
       <c r="D26" t="s">
-        <v>131</v>
+        <v>85</v>
+      </c>
+      <c r="E26">
+        <v>11</v>
       </c>
       <c r="F26" t="s">
+        <v>152</v>
+      </c>
+      <c r="I26">
+        <v>8654</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26" t="s">
         <v>132</v>
       </c>
-      <c r="G26" t="s">
-        <v>86</v>
-      </c>
-      <c r="H26">
-        <v>11</v>
-      </c>
-      <c r="I26" t="s">
-        <v>152</v>
-      </c>
-      <c r="L26">
-        <v>8654</v>
-      </c>
-      <c r="M26">
-        <v>2</v>
-      </c>
-      <c r="N26" t="s">
+      <c r="M26" t="s">
+        <v>88</v>
+      </c>
+      <c r="O26" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>133</v>
+      </c>
+      <c r="S26" t="s">
         <v>134</v>
       </c>
-      <c r="P26" t="s">
-        <v>89</v>
-      </c>
-      <c r="R26" t="s">
-        <v>90</v>
-      </c>
-      <c r="T26" t="s">
+      <c r="U26" t="s">
         <v>135</v>
       </c>
-      <c r="V26" t="s">
+      <c r="W26" t="s">
         <v>136</v>
       </c>
-      <c r="X26" t="s">
+      <c r="Y26" t="s">
         <v>137</v>
       </c>
-      <c r="Z26" t="s">
+      <c r="AA26" t="s">
         <v>138</v>
       </c>
       <c r="AB26" t="s">
         <v>139</v>
       </c>
+      <c r="AC26" t="s">
+        <v>140</v>
+      </c>
       <c r="AD26" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AE26" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AF26" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG26" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
         <f t="shared" si="0"/>
         <v>VMR1012711</v>
@@ -2651,64 +2651,64 @@
         <v>130</v>
       </c>
       <c r="D27" t="s">
-        <v>131</v>
+        <v>85</v>
+      </c>
+      <c r="E27">
+        <v>12</v>
       </c>
       <c r="F27" t="s">
+        <v>153</v>
+      </c>
+      <c r="I27">
+        <v>8654</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27" t="s">
         <v>132</v>
       </c>
-      <c r="G27" t="s">
-        <v>86</v>
-      </c>
-      <c r="H27">
-        <v>12</v>
-      </c>
-      <c r="I27" t="s">
-        <v>153</v>
-      </c>
-      <c r="L27">
-        <v>8654</v>
-      </c>
-      <c r="M27">
-        <v>2</v>
-      </c>
-      <c r="N27" t="s">
+      <c r="M27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O27" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>133</v>
+      </c>
+      <c r="S27" t="s">
         <v>134</v>
       </c>
-      <c r="P27" t="s">
-        <v>89</v>
-      </c>
-      <c r="R27" t="s">
-        <v>90</v>
-      </c>
-      <c r="T27" t="s">
+      <c r="U27" t="s">
         <v>135</v>
       </c>
-      <c r="V27" t="s">
+      <c r="W27" t="s">
         <v>136</v>
       </c>
-      <c r="X27" t="s">
+      <c r="Y27" t="s">
         <v>137</v>
       </c>
-      <c r="Z27" t="s">
+      <c r="AA27" t="s">
         <v>138</v>
       </c>
       <c r="AB27" t="s">
         <v>139</v>
       </c>
+      <c r="AC27" t="s">
+        <v>140</v>
+      </c>
       <c r="AD27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AE27" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AF27" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG27" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
         <f>HYPERLINK("https://ictv.global/id/VMR1002117","VMR1002117")</f>
         <v>VMR1002117</v>
@@ -2721,54 +2721,54 @@
         <v>154</v>
       </c>
       <c r="D28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>2844298</v>
+      </c>
+      <c r="H28">
+        <v>2877981</v>
+      </c>
+      <c r="I28">
+        <v>2954</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28" t="s">
         <v>155</v>
       </c>
-      <c r="F28" t="s">
+      <c r="M28" t="s">
+        <v>36</v>
+      </c>
+      <c r="O28" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>38</v>
+      </c>
+      <c r="S28" t="s">
+        <v>39</v>
+      </c>
+      <c r="W28" t="s">
         <v>156</v>
       </c>
-      <c r="G28" t="s">
-        <v>35</v>
-      </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
-      <c r="J28">
-        <v>2844298</v>
-      </c>
-      <c r="K28">
-        <v>2877981</v>
-      </c>
-      <c r="L28">
-        <v>2954</v>
-      </c>
-      <c r="M28">
-        <v>1</v>
-      </c>
-      <c r="N28" t="s">
+      <c r="Y28" t="s">
         <v>157</v>
       </c>
-      <c r="P28" t="s">
-        <v>37</v>
-      </c>
-      <c r="R28" t="s">
-        <v>38</v>
-      </c>
-      <c r="T28" t="s">
-        <v>39</v>
-      </c>
-      <c r="V28" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z28" t="s">
+      <c r="AA28" t="s">
         <v>158</v>
       </c>
       <c r="AB28" t="s">
         <v>159</v>
       </c>
-      <c r="AD28" t="s">
+      <c r="AE28" t="s">
         <v>160</v>
       </c>
-      <c r="AE28" t="s">
+      <c r="AF28" t="s">
         <v>161</v>
       </c>
     </row>
